--- a/astro-site/public/dl/pastry-shop-checklist-templates/BONUS-01-pastry-shop-pre-shift-meeting-template.xlsx
+++ b/astro-site/public/dl/pastry-shop-checklist-templates/BONUS-01-pastry-shop-pre-shift-meeting-template.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Planned products: viennoiserie (croissants, custard danishes, conchas...)</t>
+          <t>Planned products: viennoiserie (croissants, fruit danishes, conchas...)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Who is working today and in what position</t>
+          <t>Who is working today and in what position; anyone with vomiting, diarrhea or jaundice tells the manager and does not work with food (exclusion, FDA Food Code 2-201.11 and 2-201.12)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
